--- a/filer/16499609_munck.xlsx
+++ b/filer/16499609_munck.xlsx
@@ -615,7 +615,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision · Regnskabsår 1/10–30/9 (forskudt)</t>
         </is>
       </c>
     </row>

--- a/filer/16499609_munck.xlsx
+++ b/filer/16499609_munck.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_16499609" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_16499609" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_16499609" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_16499609" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -192,9 +193,9 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -595,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4689,6 +4690,148 @@
       </c>
       <c r="F97" s="13">
         <f>IFERROR($F$34/($F$59+$F$66)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B100" s="17">
+        <f>'pengestrom_raw_16499609'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C100" s="17">
+        <f>'pengestrom_raw_16499609'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D100" s="17">
+        <f>'pengestrom_raw_16499609'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E100" s="17">
+        <f>'pengestrom_raw_16499609'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F100" s="17">
+        <f>'pengestrom_raw_16499609'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B101" s="17">
+        <f>'pengestrom_raw_16499609'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C101" s="17">
+        <f>'pengestrom_raw_16499609'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D101" s="17">
+        <f>'pengestrom_raw_16499609'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E101" s="17">
+        <f>'pengestrom_raw_16499609'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F101" s="17">
+        <f>'pengestrom_raw_16499609'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B102" s="17">
+        <f>'pengestrom_raw_16499609'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C102" s="17">
+        <f>'pengestrom_raw_16499609'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D102" s="17">
+        <f>'pengestrom_raw_16499609'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E102" s="17">
+        <f>'pengestrom_raw_16499609'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F102" s="17">
+        <f>'pengestrom_raw_16499609'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B103" s="17">
+        <f>'pengestrom_raw_16499609'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C103" s="17">
+        <f>'pengestrom_raw_16499609'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D103" s="17">
+        <f>'pengestrom_raw_16499609'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E103" s="17">
+        <f>'pengestrom_raw_16499609'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F103" s="17">
+        <f>'pengestrom_raw_16499609'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B104">
+        <f>IF(ABS(('pengestrom_raw_16499609'!$B$2+'pengestrom_raw_16499609'!$B$3+'pengestrom_raw_16499609'!$B$4)-'pengestrom_raw_16499609'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_16499609'!$B$2+'pengestrom_raw_16499609'!$B$3+'pengestrom_raw_16499609'!$B$4)-'pengestrom_raw_16499609'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C104">
+        <f>IF(ABS(('pengestrom_raw_16499609'!$C$2+'pengestrom_raw_16499609'!$C$3+'pengestrom_raw_16499609'!$C$4)-'pengestrom_raw_16499609'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_16499609'!$C$2+'pengestrom_raw_16499609'!$C$3+'pengestrom_raw_16499609'!$C$4)-'pengestrom_raw_16499609'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D104">
+        <f>IF(ABS(('pengestrom_raw_16499609'!$D$2+'pengestrom_raw_16499609'!$D$3+'pengestrom_raw_16499609'!$D$4)-'pengestrom_raw_16499609'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_16499609'!$D$2+'pengestrom_raw_16499609'!$D$3+'pengestrom_raw_16499609'!$D$4)-'pengestrom_raw_16499609'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E104">
+        <f>IF(ABS(('pengestrom_raw_16499609'!$E$2+'pengestrom_raw_16499609'!$E$3+'pengestrom_raw_16499609'!$E$4)-'pengestrom_raw_16499609'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_16499609'!$E$2+'pengestrom_raw_16499609'!$E$3+'pengestrom_raw_16499609'!$E$4)-'pengestrom_raw_16499609'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F104">
+        <f>IF(ABS(('pengestrom_raw_16499609'!$F$2+'pengestrom_raw_16499609'!$F$3+'pengestrom_raw_16499609'!$F$4)-'pengestrom_raw_16499609'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_16499609'!$F$2+'pengestrom_raw_16499609'!$F$3+'pengestrom_raw_16499609'!$F$4)-'pengestrom_raw_16499609'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4737,334 +4880,334 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>2449292</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>3089499</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>3261760</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>4178334</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>4868635</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Produktionsomkostninger</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>2204242</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>2838459</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>2884377</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>3599912</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>4221459</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>245050</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>251040</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>377383</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>578422</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>647176</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Salgs- og distributionsomkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="16" t="n"/>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Administrationsomkostninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>146664</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>115458</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>165289</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>106968</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <v>122221</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>36564</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>16337</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>4797</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>12928</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>43237</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n">
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n">
         <v>594</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>750</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>-767</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>-1399</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>4255</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>10966</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>13017</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>6804</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>16032</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>21906</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>18760</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>13489</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>6905</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>7333</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>11052</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n">
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n">
         <v>490922</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>579416</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>41942</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>34570</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>45446</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>116995</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <v>125695</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>89964</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>81235</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>146732</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>317875</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>397727</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>1313</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>1435</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>1561</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>1611</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="17" t="n">
         <v>1608</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>105000</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>102000</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>170000</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>273000</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <v>175000</v>
       </c>
     </row>
@@ -5113,1152 +5256,1152 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Udviklingsprojekter</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Patenter, varemærker mv.</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>3918</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>6209</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>6196</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>3108</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>61</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>57</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>36</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>3979</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>7266</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>6232</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>3122</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>601</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>151522</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>124633</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>109011</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>124669</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <v>121260</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>38325</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>39441</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>85571</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>111833</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>115044</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>299249</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>295599</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>288185</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>354835</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>326813</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>4883</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>2718</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>22303</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>38542</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>19491</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>493979</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>462391</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>505070</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>629879</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>582608</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>759</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>794</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>759</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>805</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>811</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>94679</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>31435</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>22911</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>12228</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>11382</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>592637</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>501092</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>534213</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>645229</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <v>594591</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>101060</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>114757</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>147046</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>98997</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>80302</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Varer under fremstilling</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>107357</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>175069</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>162374</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>207350</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="17" t="n">
         <v>195563</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>101060</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>114757</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>147046</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>98997</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="17" t="n">
         <v>80302</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>570579</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>688645</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>733302</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>1028637</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="17" t="n">
         <v>875455</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="17" t="n">
         <v>6585</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>1804</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="17" t="n">
         <v>198</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B22" s="17" t="n">
         <v>233577</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="17" t="n">
         <v>40894</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="17" t="n">
         <v>21565</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="17" t="n">
         <v>21782</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="17" t="n">
         <v>20664</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>172</v>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>4661</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>3093</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>3198</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="F23" s="17" t="n">
         <v>8550</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
+      <c r="B24" s="17" t="n">
         <v>1934</v>
       </c>
-      <c r="C24" s="16" t="n">
+      <c r="C24" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="16" t="n">
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n">
         <v>496</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="F24" s="17" t="n">
         <v>6909</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
+      <c r="B25" s="17" t="n">
         <v>69</v>
       </c>
-      <c r="C25" s="16" t="n">
+      <c r="C25" s="17" t="n">
         <v>7946</v>
       </c>
-      <c r="D25" s="16" t="n">
+      <c r="D25" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="E25" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="16" t="n">
+      <c r="F25" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="n">
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n">
         <v>757</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="E26" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="F26" s="17" t="n">
         <v>518</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
+      <c r="B27" s="17" t="n">
         <v>951459</v>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>926024</v>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="D27" s="17" t="n">
         <v>933386</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>1269290</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="F27" s="17" t="n">
         <v>1114339</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n">
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="F28" s="17" t="n">
         <v>26641</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
+      <c r="B29" s="17" t="n">
         <v>25578</v>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="17" t="n">
         <v>80733</v>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="D29" s="17" t="n">
         <v>117562</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="17" t="n">
         <v>743986</v>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="F29" s="17" t="n">
         <v>793237</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n">
+      <c r="B30" s="17" t="n">
         <v>1078097</v>
       </c>
-      <c r="C30" s="16" t="n">
+      <c r="C30" s="17" t="n">
         <v>1121514</v>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="D30" s="17" t="n">
         <v>1197994</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="E30" s="17" t="n">
         <v>2112273</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="F30" s="17" t="n">
         <v>2014519</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n">
+      <c r="B31" s="17" t="n">
         <v>1670734</v>
       </c>
-      <c r="C31" s="16" t="n">
+      <c r="C31" s="17" t="n">
         <v>1622606</v>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="D31" s="17" t="n">
         <v>1732207</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="E31" s="17" t="n">
         <v>2757502</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="F31" s="17" t="n">
         <v>2609110</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
+      <c r="B32" s="17" t="n">
         <v>518</v>
       </c>
-      <c r="C32" s="16" t="n">
+      <c r="C32" s="17" t="n">
         <v>517</v>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="D32" s="17" t="n">
         <v>517</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="E32" s="17" t="n">
         <v>517</v>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="F32" s="17" t="n">
         <v>517</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n">
+      <c r="B33" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C33" s="16" t="n">
+      <c r="C33" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="16" t="n">
+      <c r="D33" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="E33" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="F33" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>529384</v>
       </c>
-      <c r="C37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>555670</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>599646</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>723922</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="F37" s="17" t="n">
         <v>913632</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n">
+      <c r="B38" s="17" t="n">
         <v>632030</v>
       </c>
-      <c r="C38" s="16" t="n">
+      <c r="C38" s="17" t="n">
         <v>685047</v>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="D38" s="17" t="n">
         <v>791750</v>
       </c>
-      <c r="E38" s="16" t="n">
+      <c r="E38" s="17" t="n">
         <v>1049944</v>
       </c>
-      <c r="F38" s="16" t="n">
+      <c r="F38" s="17" t="n">
         <v>1244156</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="16" t="n">
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="17" t="n">
         <v>39820</v>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="D39" s="17" t="n">
         <v>32943</v>
       </c>
-      <c r="E39" s="16" t="n">
+      <c r="E39" s="17" t="n">
         <v>104427</v>
       </c>
-      <c r="F39" s="16" t="n">
+      <c r="F39" s="17" t="n">
         <v>43896</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n">
+      <c r="B40" s="17" t="n">
         <v>47406</v>
       </c>
-      <c r="C40" s="16" t="n">
+      <c r="C40" s="17" t="n">
         <v>152598</v>
       </c>
-      <c r="D40" s="16" t="n">
+      <c r="D40" s="17" t="n">
         <v>139946</v>
       </c>
-      <c r="E40" s="16" t="n">
+      <c r="E40" s="17" t="n">
         <v>273363</v>
       </c>
-      <c r="F40" s="16" t="n">
+      <c r="F40" s="17" t="n">
         <v>279226</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Langfristede lån</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n">
+      <c r="B42" s="17" t="n">
         <v>76719</v>
       </c>
-      <c r="C42" s="16" t="n">
+      <c r="C42" s="17" t="n">
         <v>50139</v>
       </c>
-      <c r="D42" s="16" t="n">
+      <c r="D42" s="17" t="n">
         <v>47112</v>
       </c>
-      <c r="E42" s="16" t="n">
+      <c r="E42" s="17" t="n">
         <v>39044</v>
       </c>
-      <c r="F42" s="16" t="n">
+      <c r="F42" s="17" t="n">
         <v>36378</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n">
+      <c r="B43" s="17" t="n">
         <v>40215</v>
       </c>
-      <c r="C43" s="16" t="n">
+      <c r="C43" s="17" t="n">
         <v>25241</v>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="D43" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n">
+      <c r="B45" s="17" t="n">
         <v>116934</v>
       </c>
-      <c r="C45" s="16" t="n">
+      <c r="C45" s="17" t="n">
         <v>75380</v>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="D45" s="17" t="n">
         <v>47112</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="E45" s="17" t="n">
         <v>39044</v>
       </c>
-      <c r="F45" s="16" t="n">
+      <c r="F45" s="17" t="n">
         <v>36378</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n">
+      <c r="B47" s="17" t="n">
         <v>21056</v>
       </c>
-      <c r="C47" s="16" t="n">
+      <c r="C47" s="17" t="n">
         <v>24030</v>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="D47" s="17" t="n">
         <v>27993</v>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="E47" s="17" t="n">
         <v>2619</v>
       </c>
-      <c r="F47" s="16" t="n">
+      <c r="F47" s="17" t="n">
         <v>2656</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n">
+      <c r="B48" s="17" t="n">
         <v>24706</v>
       </c>
-      <c r="C48" s="16" t="n">
+      <c r="C48" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="D48" s="16" t="n">
+      <c r="D48" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E48" s="16" t="n">
+      <c r="E48" s="17" t="n">
         <v>889</v>
       </c>
-      <c r="F48" s="16" t="n">
+      <c r="F48" s="17" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="17" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n">
+      <c r="B50" s="17" t="n">
         <v>252043</v>
       </c>
-      <c r="C50" s="16" t="n">
+      <c r="C50" s="17" t="n">
         <v>248352</v>
       </c>
-      <c r="D50" s="16" t="n">
+      <c r="D50" s="17" t="n">
         <v>271032</v>
       </c>
-      <c r="E50" s="16" t="n">
+      <c r="E50" s="17" t="n">
         <v>499116</v>
       </c>
-      <c r="F50" s="16" t="n">
+      <c r="F50" s="17" t="n">
         <v>546573</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n">
+      <c r="B51" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C51" s="16" t="n">
+      <c r="C51" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D51" s="16" t="n">
+      <c r="D51" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="16" t="n">
+      <c r="E51" s="17" t="n">
         <v>3202</v>
       </c>
-      <c r="F51" s="16" t="n">
+      <c r="F51" s="17" t="n">
         <v>11124</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n"/>
-      <c r="C52" s="16" t="n"/>
-      <c r="D52" s="16" t="n"/>
-      <c r="E52" s="16" t="n"/>
-      <c r="F52" s="16" t="n"/>
+      <c r="B52" s="17" t="n"/>
+      <c r="C52" s="17" t="n"/>
+      <c r="D52" s="17" t="n"/>
+      <c r="E52" s="17" t="n"/>
+      <c r="F52" s="17" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B53" s="16" t="n">
+      <c r="B53" s="17" t="n">
         <v>8582</v>
       </c>
-      <c r="C53" s="16" t="n">
+      <c r="C53" s="17" t="n">
         <v>1003</v>
       </c>
-      <c r="D53" s="16" t="n">
+      <c r="D53" s="17" t="n">
         <v>174</v>
       </c>
-      <c r="E53" s="16" t="n">
+      <c r="E53" s="17" t="n">
         <v>123</v>
       </c>
-      <c r="F53" s="16" t="n">
+      <c r="F53" s="17" t="n">
         <v>407</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="15" t="inlineStr">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B54" s="16" t="n">
+      <c r="B54" s="17" t="n">
         <v>31634</v>
       </c>
-      <c r="C54" s="16" t="n">
+      <c r="C54" s="17" t="n">
         <v>15134</v>
       </c>
-      <c r="D54" s="16" t="n">
+      <c r="D54" s="17" t="n">
         <v>50553</v>
       </c>
-      <c r="E54" s="16" t="n">
+      <c r="E54" s="17" t="n">
         <v>42005</v>
       </c>
-      <c r="F54" s="16" t="n">
+      <c r="F54" s="17" t="n">
         <v>23695</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="15" t="inlineStr">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B55" s="16" t="n">
+      <c r="B55" s="17" t="n">
         <v>126213</v>
       </c>
-      <c r="C55" s="16" t="n">
+      <c r="C55" s="17" t="n">
         <v>109553</v>
       </c>
-      <c r="D55" s="16" t="n">
+      <c r="D55" s="17" t="n">
         <v>134529</v>
       </c>
-      <c r="E55" s="16" t="n">
+      <c r="E55" s="17" t="n">
         <v>151325</v>
       </c>
-      <c r="F55" s="16" t="n">
+      <c r="F55" s="17" t="n">
         <v>151825</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="15" t="inlineStr">
+      <c r="A56" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B56" s="16" t="n">
+      <c r="B56" s="17" t="n">
         <v>665</v>
       </c>
-      <c r="C56" s="16" t="n">
+      <c r="C56" s="17" t="n">
         <v>1002</v>
       </c>
-      <c r="D56" s="16" t="n">
+      <c r="D56" s="17" t="n">
         <v>1247</v>
       </c>
-      <c r="E56" s="16" t="n">
+      <c r="E56" s="17" t="n">
         <v>241</v>
       </c>
-      <c r="F56" s="16" t="n">
+      <c r="F56" s="17" t="n">
         <v>642</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="17" t="inlineStr">
+      <c r="A57" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B57" s="16" t="n">
+      <c r="B57" s="17" t="n">
         <v>874364</v>
       </c>
-      <c r="C57" s="16" t="n">
+      <c r="C57" s="17" t="n">
         <v>709581</v>
       </c>
-      <c r="D57" s="16" t="n">
+      <c r="D57" s="17" t="n">
         <v>753399</v>
       </c>
-      <c r="E57" s="16" t="n">
+      <c r="E57" s="17" t="n">
         <v>1395151</v>
       </c>
-      <c r="F57" s="16" t="n">
+      <c r="F57" s="17" t="n">
         <v>1049350</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="17" t="inlineStr">
+      <c r="A58" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B58" s="16" t="n">
+      <c r="B58" s="17" t="n">
         <v>991298</v>
       </c>
-      <c r="C58" s="16" t="n">
+      <c r="C58" s="17" t="n">
         <v>784961</v>
       </c>
-      <c r="D58" s="16" t="n">
+      <c r="D58" s="17" t="n">
         <v>800511</v>
       </c>
-      <c r="E58" s="16" t="n">
+      <c r="E58" s="17" t="n">
         <v>1434195</v>
       </c>
-      <c r="F58" s="16" t="n">
+      <c r="F58" s="17" t="n">
         <v>1085728</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="17" t="inlineStr">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B59" s="16" t="n">
+      <c r="B59" s="17" t="n">
         <v>1670734</v>
       </c>
-      <c r="C59" s="16" t="n">
+      <c r="C59" s="17" t="n">
         <v>1622606</v>
       </c>
-      <c r="D59" s="16" t="n">
+      <c r="D59" s="17" t="n">
         <v>1732207</v>
       </c>
-      <c r="E59" s="16" t="n">
+      <c r="E59" s="17" t="n">
         <v>2757502</v>
       </c>
-      <c r="F59" s="16" t="n">
+      <c r="F59" s="17" t="n">
         <v>2609110</v>
       </c>
     </row>
@@ -6268,6 +6411,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>31167</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>150246</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>282202</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>1055290</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>602891</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>14986</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>36251</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-146254</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-223739</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-82599</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-18308</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>-106299</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-90482</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-154687</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-240940</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
